--- a/Stock Analysis/RodWal Terminal/Project Management.xlsx
+++ b/Stock Analysis/RodWal Terminal/Project Management.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Analysis/RodWal Terminal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_F25DC773A252ABDACC1048DC8198614A5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6040202E-5385-4CB2-BEB8-6A085E6A4CE8}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_F25DC773A252ABDACC1048DC8198614A5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00D05614-A5D5-4382-93DB-735B6C305E42}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scope" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="71">
   <si>
     <t>RodWal Terminal.py</t>
   </si>
@@ -101,14 +101,216 @@
   </si>
   <si>
     <t>IBIT</t>
+  </si>
+  <si>
+    <t>📋 RodWal Terminal – Folder &amp; File Structure Table</t>
+  </si>
+  <si>
+    <t>Folder</t>
+  </si>
+  <si>
+    <t>Subfolder/File</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>rodwal_terminal/</t>
+  </si>
+  <si>
+    <t>(Project Root)</t>
+  </si>
+  <si>
+    <t>Main application directory</t>
+  </si>
+  <si>
+    <t>core/</t>
+  </si>
+  <si>
+    <t>Initialization file for core module</t>
+  </si>
+  <si>
+    <t>Stores Terminal's colour palette</t>
+  </si>
+  <si>
+    <t>config.py</t>
+  </si>
+  <si>
+    <t>Application settings and configuration</t>
+  </si>
+  <si>
+    <t>logging.py</t>
+  </si>
+  <si>
+    <t>Logging setup and configuration</t>
+  </si>
+  <si>
+    <t>scheduler.py</t>
+  </si>
+  <si>
+    <t>Periodic job scheduler</t>
+  </si>
+  <si>
+    <t>data_providers/</t>
+  </si>
+  <si>
+    <t>Initialization file for data providers</t>
+  </si>
+  <si>
+    <t>base.py</t>
+  </si>
+  <si>
+    <t>Base class for market data APIs</t>
+  </si>
+  <si>
+    <t>yahoo.py</t>
+  </si>
+  <si>
+    <t>Yahoo Finance integration</t>
+  </si>
+  <si>
+    <r>
+      <t>polygon.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(optional)</t>
+    </r>
+  </si>
+  <si>
+    <t>Polygon.io integration</t>
+  </si>
+  <si>
+    <t>modules/</t>
+  </si>
+  <si>
+    <t>Initialization file for domain modules</t>
+  </si>
+  <si>
+    <t>Market overview and data logic</t>
+  </si>
+  <si>
+    <t>portfolio.py</t>
+  </si>
+  <si>
+    <t>Portfolio management logic</t>
+  </si>
+  <si>
+    <t>screener.py</t>
+  </si>
+  <si>
+    <t>Stock screener functionality</t>
+  </si>
+  <si>
+    <t>news.py</t>
+  </si>
+  <si>
+    <t>News aggregation and processing</t>
+  </si>
+  <si>
+    <t>econ.py</t>
+  </si>
+  <si>
+    <t>Economic indicators and data</t>
+  </si>
+  <si>
+    <t>ui/</t>
+  </si>
+  <si>
+    <t>terminal.py</t>
+  </si>
+  <si>
+    <t>Tkinter shell and command router</t>
+  </si>
+  <si>
+    <t>views/</t>
+  </si>
+  <si>
+    <t>UI views and widgets</t>
+  </si>
+  <si>
+    <t>views/*.py</t>
+  </si>
+  <si>
+    <t>Individual view components</t>
+  </si>
+  <si>
+    <t>config/</t>
+  </si>
+  <si>
+    <t>markets.json</t>
+  </si>
+  <si>
+    <t>Market watchlist configuration</t>
+  </si>
+  <si>
+    <t>settings.json</t>
+  </si>
+  <si>
+    <t>User preferences and settings</t>
+  </si>
+  <si>
+    <t>tests/</t>
+  </si>
+  <si>
+    <t>test_*.py</t>
+  </si>
+  <si>
+    <t>Unit and integration tests</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -136,10 +338,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,7 +642,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -433,8 +650,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E594864B-D80B-48F9-9815-13C50CA790C4}">
-  <dimension ref="B1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:F37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -442,27 +659,27 @@
     <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6">
       <c r="F1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6">
       <c r="C3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6">
       <c r="D4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6">
       <c r="D5" t="s">
         <v>2</v>
       </c>
@@ -470,19 +687,247 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6">
       <c r="C8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6">
       <c r="D9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6">
       <c r="D10" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="18">
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="30">
+      <c r="B15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="45">
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="45">
+      <c r="B17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="45">
+      <c r="B18" s="5"/>
+      <c r="C18" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="45">
+      <c r="B19" s="5"/>
+      <c r="C19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="45">
+      <c r="B20" s="5"/>
+      <c r="C20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="30">
+      <c r="B21" s="5"/>
+      <c r="C21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="45">
+      <c r="B22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="45">
+      <c r="B23" s="5"/>
+      <c r="C23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="30">
+      <c r="B24" s="5"/>
+      <c r="C24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="57.75">
+      <c r="B25" s="5"/>
+      <c r="C25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="45">
+      <c r="B26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="45">
+      <c r="B27" s="5"/>
+      <c r="C27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="45">
+      <c r="B28" s="5"/>
+      <c r="C28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="30">
+      <c r="B29" s="5"/>
+      <c r="C29" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="45">
+      <c r="B30" s="5"/>
+      <c r="C30" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="45">
+      <c r="B31" s="5"/>
+      <c r="C31" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="45">
+      <c r="B32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="30">
+      <c r="B33" s="5"/>
+      <c r="C33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="30">
+      <c r="B34" s="5"/>
+      <c r="C34" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="45">
+      <c r="B35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="45">
+      <c r="B36" s="5"/>
+      <c r="C36" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="45">
+      <c r="B37" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -493,7 +938,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B991FB6D-2CFA-41B6-B8FA-B78030F02C77}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
@@ -502,7 +947,7 @@
     <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -519,12 +964,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -541,7 +986,7 @@
         <v>0.88055555555555554</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -558,7 +1003,7 @@
         <v>0.88055555555555554</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -575,7 +1020,7 @@
         <v>0.88055555555555554</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +1037,7 @@
         <v>0.88055555555555554</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -609,7 +1054,7 @@
         <v>0.88055555555555554</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -626,7 +1071,7 @@
         <v>0.88055555555555554</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>20</v>
       </c>
